--- a/radio/copy.xlsx
+++ b/radio/copy.xlsx
@@ -3,22 +3,36 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A745231-D636-4094-8738-733EA1AEC6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31471D9-6848-455D-A22E-2C586D993A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
     <sheet name="DE" sheetId="2" r:id="rId2"/>
     <sheet name="BR" sheetId="3" r:id="rId3"/>
     <sheet name="KR" sheetId="4" r:id="rId4"/>
+    <sheet name="CA_FR" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="410">
   <si>
     <t>Type</t>
   </si>
@@ -1302,6 +1316,312 @@
   </si>
   <si>
     <t>나만의 노래 만드는 방법 4단계 영상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Créez des chansons et répandez la joie avec Radio Optimism</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Défiler vers le bas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme portant une veste de randonnée rouge se tient à un endroit d’où on peut voir un vaste océan et des montagnes enneigées.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Logo de la campagne de Radio Optimism</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ceci est un contenu vidéo de Radio Optimism de LG sur la chaîne YouTube de LG Electronics.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chaque jour, nous faisons défiler et glisser l’écran, et tapons sur des « j’aime ». &lt;br&gt;
+        &lt;span class="radio-highlight"&gt;Mais établissons-nous vraiment des liens avec les autres?&lt;/span&gt;&lt;br&gt;
+         Ce dont nous avons besoin, ce sont peut-être des relations de cœur à cœur.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C’est pourquoi nous transmettons notre message « La vie est belle »&lt;br&gt;
+au moyen du langage universel de la musique. &lt;br&gt;
+Créez une mélodie pour la personne qui vous est chère avec Radio Optimism de LG. &lt;br&gt;
+C’est facile! Pensez à quelqu’un de spécial et écrivez quelques mots à son sujet.&lt;br&gt;
+Une chanson unique sera ensuite créée, prête à être partagée avec un sourire.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Composer une chanson sincère pour quelqu’un
+et recevoir un morceau d’un être cher sont des moments authentiques
+qui nous permettent de réaffirmer que La vie est belle.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une jeune femme vêtue d’un chandail blanc et d’un jean est allongée sur un divan; elle met un « j’aime » avec son téléphone au contenu que son amie a publié sur les médias sociaux.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un jeune homme et une jeune femme sont assis à un bureau et visionnent la campagne Radio Optimism sur un ordinateur portable.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Une femme sourit en regardant son ordinateur portable dans une pièce spacieuse.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Créez votre chanson maintenant.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://radiooptimism.lg.com/fr?referrer_locale=fr&amp;referrer_site=lifesgood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comment créer votre chanson</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Il suffit d’appuyer sur quelques touches – c’est aussi simple que cela.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accédez à la plateforme Radio Optimism.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Appuyez sur « Alors, on le crée, ce hit ? » pour vous inscrire et commencer votre histoire.
+Choisissez votre langue de préférence pour commencer.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vidéo de l’étape 1 de la rubrique Comment créer une chanson</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Racontez votre histoire.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qui êtes-vous et à qui cette chanson est-elle destinée?&lt;br&gt;
+Plus vous partagez de choses – un souvenir, un moment, ou quelque chose que vous êtes les seuls à connaître – meilleures seront vos paroles. Une fois que vous avez terminé, nous transformerons le tout en une piste accompagnée d’une pochette de disque personnalisée.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vidéo de l’étape 2 de la rubrique Comment créer une chanson</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choisissez votre style.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintenant, choisissez votre sonorité. Choisissez un genre – du hip-hop à la K-pop – et un style qui correspond à votre histoire.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vidéo de l’étape 3 de la rubrique Comment créer une chanson</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Votre chanson est prête!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Envoyez-la à quelqu’un ㅡ et laissez-la jouer sur Radio Optimism.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vidéo de l’étape 4 de la rubrique Comment créer une chanson</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Des chansons faites pour vous</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un rayon de positivité</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Par LG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque Un rayon de positivité, créée par LG grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque longue durée Un rayon de positivité, créée par LG grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio Un rayon de positivité, créée par LG grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player:Un rayon de positivité</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player: 100 ans de notre arrière-grand-mère!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100 ans de notre arrière-grand-mère!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Par Arrière-petit-fils</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque 100 ans de notre arrière-grand-mère!, créée par Arrière-petit-fils grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque 100 ans de notre arrière-grand-mère!, créée par Arrière-petit-fils grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio 100 ans de notre arrière-grand-mère!, créée par Arrière-petit-fils grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player: Note parfaite! Tous ces efforts ont payé!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note parfaite! Tous ces efforts ont payé!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Par Parents</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque Note parfaite! Tous ces efforts ont payé!, créée par Parents grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque longue durée Note parfaite! Tous ces efforts ont payé!, créée par Parents grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio Note parfaite! Tous ces efforts ont payé!, créée par Parents grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player: Le yoga a transformé ma vie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Le yoga a transformé ma vie</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Par Élève</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque Le yoga a transformé ma vie, créée par Élève grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque longue durée Le yoga a transformé ma vie, créée par Élève grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio Le yoga a transformé ma vie, créée par Élève grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player: Un an sans cancer!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Un an sans cancer!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Par Survivant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque Un an sans cancer!, créée par Survivant grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque longue durée Un an sans cancer!, créée par Survivant grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio Un an sans cancer!, créée par Survivant grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notre petit-fils est né!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player: Notre petit-fils est né!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Par Grands-parents</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque Notre petit-fils est né!, créée par Grands-parents grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque longue durée Notre petit-fils est né!, créée par Grands-parents grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio Notre petit-fils est né!, créée par Grands-parents grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audio player: Répandre la joie, répandre la lumière</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Répandre la joie, répandre la lumière</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La pochette du disque Répandre la joie, répandre la lumière, créée par LG grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L’image du disque longue durée Répandre la joie, répandre la lumière, créée par LG grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>La piste audio Répandre la joie, répandre la lumière, créée par LG grâce à l’IA.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LA STATION DE LA DÉDICACE 24 h/24, 7 j/7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sur le côté droit de la bannière, on voit diverses icônes liées à Radio Optimism et à La vie est belle.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sur le côté gauche de la bannière, on voit diverses icônes liées à Radio Optimism et à La vie est belle.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>* Certains contenus ont été générés à l’aide de l’IA à des fins de représentation.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>* Les langues prises en charge peuvent varier selon le pays ou la région.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4832,4 +5152,754 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F931AEE-808B-4058-B0D8-03858E1E6C20}">
+  <dimension ref="A1:B98"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="50.65" x14ac:dyDescent="0.6">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="84.4" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="50.65" x14ac:dyDescent="0.6">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="50.65" x14ac:dyDescent="0.6">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A55" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A61" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A63" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A64" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A65" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A79" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A81" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A83" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A86" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A88" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A90" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A96" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A97" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B76" r:id="rId1" xr:uid="{D86ADF52-C6B8-405B-B3DF-3EBCE218E447}"/>
+    <hyperlink ref="B78" r:id="rId2" xr:uid="{F3AEEAF2-6E87-4099-8C7C-3AED62F3D207}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>